--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
